--- a/data.xlsx
+++ b/data.xlsx
@@ -1,32 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysj90\Desktop\자료\jinny\web-github\artworks\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D32477-6C43-447B-86A1-CEF82CA965E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet state="visible" name="Sheet2" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="BZsF9G7WcBaL244LAVRD2zgK4By9VRDBJS1RibGn/ZE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="KK7jxAVPh2ew51QaoEjNzPRwZX+YVpHV4TofOVXSWo4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="215">
   <si>
     <t>[site]</t>
   </si>
@@ -52,6 +43,9 @@
     <t>artistName</t>
   </si>
   <si>
+    <t>Jiyoo Han</t>
+  </si>
+  <si>
     <t>Contact 섹션 등에 표시될 작가 이름</t>
   </si>
   <si>
@@ -88,15 +82,42 @@
     <t>이미지파일명</t>
   </si>
   <si>
+    <t>Around here</t>
+  </si>
+  <si>
+    <t>224.2x162.2cm</t>
+  </si>
+  <si>
+    <t>Acrylic on Canvas</t>
+  </si>
+  <si>
+    <t>dusty_Around here_1_200P.jpg</t>
+  </si>
+  <si>
+    <t>Alleyway</t>
+  </si>
+  <si>
+    <t>162.2x97cm</t>
+  </si>
+  <si>
+    <t>dusty_Alleyway_100M.jpg</t>
+  </si>
+  <si>
+    <t>Happy Merry Christmas</t>
+  </si>
+  <si>
+    <t>130.0x162.2cm</t>
+  </si>
+  <si>
+    <t>dusty_Happy Merry Christmas_100F.jpg</t>
+  </si>
+  <si>
     <t>Home sweet home</t>
   </si>
   <si>
     <t>116.8x91.0cm</t>
   </si>
   <si>
-    <t>Acrylic on Canvas</t>
-  </si>
-  <si>
     <t>dusty_Home sweet home_50F.jpg</t>
   </si>
   <si>
@@ -109,6 +130,9 @@
     <t>Simpson’s house</t>
   </si>
   <si>
+    <t>dusty_Simpson's house_50F.jpg</t>
+  </si>
+  <si>
     <t>Yarn box</t>
   </si>
   <si>
@@ -142,6 +166,9 @@
     <t>80.3x65.1cm</t>
   </si>
   <si>
+    <t>dusty_Simpson's Living room_20F.jpg</t>
+  </si>
+  <si>
     <t>Very Dusty</t>
   </si>
   <si>
@@ -259,9 +286,27 @@
     <t>dusty_home home_1_1S.jpg / dusty_home home_2_1S.jpg</t>
   </si>
   <si>
+    <t>Camp</t>
+  </si>
+  <si>
+    <t>27.3x22cm</t>
+  </si>
+  <si>
+    <t>dusty_Camp_3F.jpg</t>
+  </si>
+  <si>
     <t>Hideaway</t>
   </si>
   <si>
+    <t>130.3×162.2cm</t>
+  </si>
+  <si>
+    <t>Oil pastel on paper</t>
+  </si>
+  <si>
+    <t>Hideaway_01_100F.jpg</t>
+  </si>
+  <si>
     <t>Oil pastel on Canvas</t>
   </si>
   <si>
@@ -271,81 +316,195 @@
     <t>BODY_002_50F.JPG</t>
   </si>
   <si>
+    <t>65.1x80.3cm</t>
+  </si>
+  <si>
+    <t>Hideaway_04_25F.jpg</t>
+  </si>
+  <si>
+    <t>Body drawing 1</t>
+  </si>
+  <si>
+    <t>Oil pastel on Paper</t>
+  </si>
+  <si>
     <t>Body_drawing_001.jpg</t>
   </si>
   <si>
+    <t>Body drawing 2</t>
+  </si>
+  <si>
     <t>Body_drawing_002.jpg</t>
   </si>
   <si>
+    <t>Body drawing 3</t>
+  </si>
+  <si>
     <t>Body_drawing_003.jpg</t>
   </si>
   <si>
+    <t>Body drawing 4</t>
+  </si>
+  <si>
     <t>Body_drawing_004.jpg</t>
   </si>
   <si>
+    <t>Body drawing 5</t>
+  </si>
+  <si>
     <t>Body_drawing_005.jpg</t>
   </si>
   <si>
+    <t>Body drawing 6</t>
+  </si>
+  <si>
     <t>Body_drawing_006.jpg</t>
   </si>
   <si>
+    <t>Body drawing 7</t>
+  </si>
+  <si>
     <t>Body_drawing_007.jpg</t>
   </si>
   <si>
+    <t>Body drawing 8</t>
+  </si>
+  <si>
     <t>Body_drawing_008.jpg</t>
   </si>
   <si>
+    <t>Body drawing 9</t>
+  </si>
+  <si>
     <t>Body_drawing_009.jpg</t>
   </si>
   <si>
+    <t>Body drawing 10</t>
+  </si>
+  <si>
     <t>Body_drawing_010.jpg</t>
   </si>
   <si>
+    <t>Body drawing 11</t>
+  </si>
+  <si>
     <t>Body_drawing_011.jpg</t>
   </si>
   <si>
+    <t>Body drawing 12</t>
+  </si>
+  <si>
     <t>Body_drawing_012.jpg</t>
   </si>
   <si>
+    <t>Body drawing 13</t>
+  </si>
+  <si>
     <t>Body_drawing_013.jpg</t>
   </si>
   <si>
+    <t>Body drawing 14</t>
+  </si>
+  <si>
     <t>Body_drawing_014.jpg</t>
   </si>
   <si>
+    <t>Body drawing 15</t>
+  </si>
+  <si>
     <t>Body_drawing_015.jpg</t>
   </si>
   <si>
+    <t>Body drawing 16</t>
+  </si>
+  <si>
     <t>Body_drawing_016.jpg</t>
   </si>
   <si>
+    <t>Body drawing 17</t>
+  </si>
+  <si>
     <t>Body_drawing_017.jpg</t>
   </si>
   <si>
+    <t>Body drawing 18</t>
+  </si>
+  <si>
     <t>Body_drawing_018.jpg</t>
   </si>
   <si>
+    <t>Body drawing 19</t>
+  </si>
+  <si>
     <t>Body_drawing_019.jpg</t>
   </si>
   <si>
+    <t>Body drawing 20</t>
+  </si>
+  <si>
     <t>Body_drawing_020.jpg</t>
   </si>
   <si>
+    <t>Body drawing 21</t>
+  </si>
+  <si>
     <t>Body_drawing_021.jpg</t>
   </si>
   <si>
+    <t>Body drawing 22</t>
+  </si>
+  <si>
     <t>Body_drawing_022.jpg</t>
   </si>
   <si>
+    <t>Body drawing 23</t>
+  </si>
+  <si>
     <t>Body_drawing_023.jpg</t>
   </si>
   <si>
+    <t>Body drawing 24</t>
+  </si>
+  <si>
     <t>Body_drawing_024.jpg</t>
   </si>
   <si>
+    <t>Body drawing 25</t>
+  </si>
+  <si>
     <t>Body_drawing_025.jpg</t>
   </si>
   <si>
+    <t>Wetland_1</t>
+  </si>
+  <si>
+    <t>Oil on Canvas</t>
+  </si>
+  <si>
+    <t>wetland_1_50S.jpg</t>
+  </si>
+  <si>
+    <t>Wetland_2</t>
+  </si>
+  <si>
+    <t>Wetland_2_30F.jpg</t>
+  </si>
+  <si>
+    <t>Glacial Striation_Crevasse_1</t>
+  </si>
+  <si>
+    <t>Mixed media on Panel</t>
+  </si>
+  <si>
+    <t>Crevasse_1_25F.jpg</t>
+  </si>
+  <si>
+    <t>Glacial Striation_Crevasse_2</t>
+  </si>
+  <si>
+    <t>Crevasse_2_10F.jpg</t>
+  </si>
+  <si>
     <t>[cv]</t>
   </si>
   <si>
@@ -503,54 +662,28 @@
   </si>
   <si>
     <t>2020 XX재단 신진작가 지원 프로그램 선정</t>
-  </si>
-  <si>
-    <t>Han Jiyoo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dusty_Simpson_s Living room_20F.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dusty_Simpson_s house_50F.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Body drawing</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -558,17 +691,11 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -582,35 +709,42 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+  <cellXfs count="6">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -800,31 +934,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1024"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="86.26953125" customWidth="1"/>
-    <col min="3" max="3" width="32.7265625" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" customWidth="1"/>
-    <col min="6" max="6" width="61.7265625" customWidth="1"/>
-    <col min="7" max="26" width="8.7265625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.29"/>
+    <col customWidth="1" min="2" max="2" width="86.29"/>
+    <col customWidth="1" min="3" max="3" width="32.71"/>
+    <col customWidth="1" min="4" max="4" width="20.0"/>
+    <col customWidth="1" min="5" max="5" width="5.71"/>
+    <col customWidth="1" min="6" max="6" width="61.71"/>
+    <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" customHeight="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.5" customHeight="1">
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -835,7 +969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1">
+    <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -846,970 +980,1252 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16.5" customHeight="1">
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1"/>
+    <row r="7" ht="16.5" customHeight="1"/>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1">
+      <c r="A10" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2026.0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customHeight="1">
+      <c r="A20" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
+      <c r="A21" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1">
+      <c r="A23" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1">
+      <c r="A24" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1">
+      <c r="A25" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1">
+      <c r="A26" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2021.0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1">
+      <c r="A27" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2022.0</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1">
+      <c r="A28" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1">
+      <c r="A29" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2026.0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1">
+      <c r="A30" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" customHeight="1">
+      <c r="A31" s="3">
+        <v>22.0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1">
+      <c r="A32" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
+      <c r="A33" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2024.0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
+      <c r="A34" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2026.0</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1">
+      <c r="A35" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2026.0</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" s="3">
+        <v>27.0</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1">
+      <c r="A38" s="3">
+        <v>29.0</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2026.0</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1">
+      <c r="A39" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1">
+      <c r="A40" s="3">
+        <v>31.0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1">
+      <c r="A41" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1">
+      <c r="A42" s="3">
+        <v>33.0</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1">
+      <c r="A43" s="3">
+        <v>34.0</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1">
+      <c r="A44" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
+      <c r="A45" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1">
+      <c r="A46" s="3">
+        <v>37.0</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1">
+      <c r="A47" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1">
+      <c r="A48" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1">
+      <c r="A49" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" customHeight="1">
+      <c r="A50" s="3">
+        <v>41.0</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" customHeight="1">
+      <c r="A51" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1">
+      <c r="A52" s="3">
+        <v>43.0</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="A53" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E53" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" customHeight="1">
+      <c r="A54" s="3">
+        <v>45.0</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1">
+      <c r="A55" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1">
+      <c r="A56" s="3">
+        <v>47.0</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" customHeight="1">
+      <c r="A57" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" customHeight="1">
+      <c r="A58" s="3">
+        <v>49.0</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" customHeight="1">
+      <c r="A59" s="3">
+        <v>50.0</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" customHeight="1">
+      <c r="A60" s="3">
+        <v>51.0</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" customHeight="1">
+      <c r="A61" s="3">
+        <v>52.0</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" customHeight="1">
+      <c r="A62" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" customHeight="1">
+      <c r="A63" s="3">
+        <v>54.0</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E63" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" customHeight="1">
+      <c r="A64" s="3">
+        <v>55.0</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E64" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" customHeight="1">
+      <c r="A65" s="3">
+        <v>56.0</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1">
+      <c r="A66" s="3">
+        <v>57.0</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A10" s="2">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A11" s="2">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A12" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F12" s="2" t="s">
+    </row>
+    <row r="67" ht="16.5" customHeight="1">
+      <c r="A67" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" s="4">
+        <v>2025.0</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A13" s="2">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A14" s="2">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A15" s="2">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A16" s="2">
-        <v>7</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A17" s="2">
-        <v>8</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A18" s="2">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A19" s="2">
-        <v>10</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2023</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A20" s="2">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A21" s="2">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A22" s="2">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A23" s="2">
-        <v>14</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2021</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A24" s="2">
-        <v>15</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="2">
-        <v>2022</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A25" s="2">
-        <v>16</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A26" s="2">
-        <v>17</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2026</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A27" s="2">
-        <v>18</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A28" s="2">
-        <v>19</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A29" s="2">
-        <v>20</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A30" s="2">
-        <v>21</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2024</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A31" s="2">
-        <v>22</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A32" s="2">
-        <v>23</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2025</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A33" s="2">
-        <v>24</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="68" ht="16.5" customHeight="1"/>
+    <row r="69" ht="16.5" customHeight="1"/>
+    <row r="70" ht="16.5" customHeight="1"/>
+    <row r="71" ht="16.5" customHeight="1"/>
+    <row r="72" ht="16.5" customHeight="1"/>
+    <row r="73" ht="16.5" customHeight="1">
+      <c r="A73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A34" s="2">
-        <v>25</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A35" s="2">
-        <v>26</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A36" s="2">
-        <v>27</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A37" s="2">
-        <v>28</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A38" s="2">
-        <v>29</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A39" s="2">
-        <v>30</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A40" s="2">
-        <v>31</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A41" s="2">
-        <v>32</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A42" s="2">
-        <v>33</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A43" s="2">
-        <v>34</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A44" s="2">
-        <v>35</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A45" s="2">
-        <v>36</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A46" s="2">
-        <v>37</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A47" s="2">
-        <v>38</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A48" s="2">
-        <v>39</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A49" s="2">
-        <v>40</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A50" s="2">
-        <v>41</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A51" s="2">
-        <v>42</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A52" s="2">
-        <v>43</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A53" s="2">
-        <v>44</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A54" s="2">
-        <v>45</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A55" s="2">
-        <v>46</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A56" s="2">
-        <v>47</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A57" s="2">
-        <v>48</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="59" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="60" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="61" spans="1:6" ht="16.5" customHeight="1"/>
-    <row r="62" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="16.5" customHeight="1">
-      <c r="B63" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="16.5" customHeight="1">
-      <c r="B64" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="67" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B67" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B68" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B69" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B70" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B71" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B72" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B73" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" ht="16.5" customHeight="1">
+      <c r="B73" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1">
       <c r="B74" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B75" s="2"/>
-    </row>
-    <row r="76" spans="2:2" ht="16.5" customHeight="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1">
+      <c r="B75" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" customHeight="1">
       <c r="B76" s="2"/>
     </row>
-    <row r="77" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B77" s="2"/>
-    </row>
-    <row r="78" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B78" s="2"/>
-    </row>
-    <row r="79" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B79" s="2"/>
-    </row>
-    <row r="80" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B80" s="2"/>
-    </row>
-    <row r="81" spans="2:2" ht="16.5" customHeight="1">
-      <c r="B81" s="2"/>
-    </row>
-    <row r="82" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="83" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="84" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="85" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="86" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="87" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="88" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="89" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="90" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="91" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="92" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="93" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="94" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="95" spans="2:2" ht="16.5" customHeight="1"/>
-    <row r="96" spans="2:2" ht="16.5" customHeight="1"/>
+    <row r="77" ht="16.5" customHeight="1"/>
+    <row r="78" ht="16.5" customHeight="1">
+      <c r="B78" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" customHeight="1">
+      <c r="B79" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" customHeight="1">
+      <c r="B80" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" customHeight="1">
+      <c r="B81" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" customHeight="1">
+      <c r="B82" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" customHeight="1">
+      <c r="B83" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" customHeight="1">
+      <c r="B84" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" customHeight="1">
+      <c r="B85" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1">
+      <c r="B86" s="2"/>
+    </row>
+    <row r="87" ht="16.5" customHeight="1">
+      <c r="B87" s="2"/>
+    </row>
+    <row r="88" ht="16.5" customHeight="1">
+      <c r="B88" s="2"/>
+    </row>
+    <row r="89" ht="16.5" customHeight="1">
+      <c r="B89" s="2"/>
+    </row>
+    <row r="90" ht="16.5" customHeight="1">
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91" ht="16.5" customHeight="1">
+      <c r="B91" s="2"/>
+    </row>
+    <row r="92" ht="16.5" customHeight="1">
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93" ht="16.5" customHeight="1"/>
+    <row r="94" ht="16.5" customHeight="1"/>
+    <row r="95" ht="16.5" customHeight="1"/>
+    <row r="96" ht="16.5" customHeight="1"/>
     <row r="97" ht="16.5" customHeight="1"/>
     <row r="98" ht="16.5" customHeight="1"/>
     <row r="99" ht="16.5" customHeight="1"/>
@@ -2738,293 +3154,307 @@
     <row r="1022" ht="16.5" customHeight="1"/>
     <row r="1023" ht="16.5" customHeight="1"/>
     <row r="1024" ht="16.5" customHeight="1"/>
+    <row r="1025" ht="16.5" customHeight="1"/>
+    <row r="1026" ht="16.5" customHeight="1"/>
+    <row r="1027" ht="16.5" customHeight="1"/>
+    <row r="1028" ht="16.5" customHeight="1"/>
+    <row r="1029" ht="16.5" customHeight="1"/>
+    <row r="1030" ht="16.5" customHeight="1"/>
+    <row r="1031" ht="16.5" customHeight="1"/>
+    <row r="1032" ht="16.5" customHeight="1"/>
+    <row r="1033" ht="16.5" customHeight="1"/>
+    <row r="1034" ht="16.5" customHeight="1"/>
+    <row r="1035" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="26" width="8.7265625" customWidth="1"/>
+    <col customWidth="1" min="1" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.5" customHeight="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="16.5" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="16.5" customHeight="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="16.5" customHeight="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="16.5" customHeight="1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="16.5" customHeight="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="16.5" customHeight="1">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="16.5" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="10" spans="1:1" ht="16.5" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1"/>
+    <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="16.5" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="16.5" customHeight="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="16.5" customHeight="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="16.5" customHeight="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="16.5" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="17" spans="1:1" ht="16.5" customHeight="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1"/>
+    <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="16.5" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="16.5" customHeight="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="16.5" customHeight="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="16.5" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="16.5" customHeight="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.5" customHeight="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="16.5" customHeight="1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="16.5" customHeight="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="16.5" customHeight="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="16.5" customHeight="1">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="16.5" customHeight="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="16.5" customHeight="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:1" ht="16.5" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1"/>
+    <row r="31" ht="16.5" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="16.5" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="16.5" customHeight="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="16.5" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="16.5" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="16.5" customHeight="1">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="16.5" customHeight="1">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="16.5" customHeight="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="40" spans="1:1" ht="16.5" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1"/>
+    <row r="40" ht="16.5" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="16.5" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="16.5" customHeight="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="16.5" customHeight="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="16.5" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="16.5" customHeight="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="16.5" customHeight="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="16.5" customHeight="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="16.5" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="50" spans="1:1" ht="16.5" customHeight="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1"/>
+    <row r="50" ht="16.5" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="16.5" customHeight="1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="16.5" customHeight="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="16.5" customHeight="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="16.5" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="16.5" customHeight="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="16.5" customHeight="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="16.5" customHeight="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="59" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="60" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="61" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="62" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="63" spans="1:1" ht="16.5" customHeight="1"/>
-    <row r="64" spans="1:1" ht="16.5" customHeight="1"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" customHeight="1"/>
+    <row r="59" ht="16.5" customHeight="1"/>
+    <row r="60" ht="16.5" customHeight="1"/>
+    <row r="61" ht="16.5" customHeight="1"/>
+    <row r="62" ht="16.5" customHeight="1"/>
+    <row r="63" ht="16.5" customHeight="1"/>
+    <row r="64" ht="16.5" customHeight="1"/>
     <row r="65" ht="16.5" customHeight="1"/>
     <row r="66" ht="16.5" customHeight="1"/>
     <row r="67" ht="16.5" customHeight="1"/>
@@ -3962,8 +4392,9 @@
     <row r="999" ht="16.5" customHeight="1"/>
     <row r="1000" ht="16.5" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -10,14 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="KK7jxAVPh2ew51QaoEjNzPRwZX+YVpHV4TofOVXSWo4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="GuQ77+muXCzyV2xgxHtCddnD5xQmDOymYu3SIenguUI="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
   <si>
     <t>[site]</t>
   </si>
@@ -130,7 +130,7 @@
     <t>Simpson’s house</t>
   </si>
   <si>
-    <t>dusty_Simpson's house_50F.jpg</t>
+    <t>dusty_Simpson_s house_50F.jpg</t>
   </si>
   <si>
     <t>Yarn box</t>
@@ -166,7 +166,7 @@
     <t>80.3x65.1cm</t>
   </si>
   <si>
-    <t>dusty_Simpson's Living room_20F.jpg</t>
+    <t>dusty_Simpson_s Living room_20F.jpg</t>
   </si>
   <si>
     <t>Very Dusty</t>
@@ -293,6 +293,27 @@
   </si>
   <si>
     <t>dusty_Camp_3F.jpg</t>
+  </si>
+  <si>
+    <t>Merry-go-round</t>
+  </si>
+  <si>
+    <t>33.4x24.2cm</t>
+  </si>
+  <si>
+    <t>dusty_Merry-go-round.jpg</t>
+  </si>
+  <si>
+    <t>Claw Machine</t>
+  </si>
+  <si>
+    <t>dusty_Claw Machine.jpg</t>
+  </si>
+  <si>
+    <t>Book Store</t>
+  </si>
+  <si>
+    <t>dusty_Book Store.jpg</t>
   </si>
   <si>
     <t>Hideaway</t>
@@ -686,12 +707,18 @@
       <name val="Malgun Gothic"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -714,7 +741,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -723,6 +750,10 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1533,83 +1564,143 @@
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>26.0</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1">
+      <c r="A36" s="4">
+        <v>27.0</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="4">
         <v>2026.0</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="F36" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="3">
-        <v>2025.0</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" s="3">
-        <v>2025.0</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="C37" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2026.0</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>98</v>
       </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="3">
         <v>29.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E38" s="3">
         <v>2026.0</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1">
@@ -1617,17 +1708,19 @@
         <v>30.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="D39" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E39" s="3">
         <v>2025.0</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1">
@@ -1635,11 +1728,13 @@
         <v>31.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="D40" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E40" s="3">
         <v>2025.0</v>
@@ -1653,14 +1748,16 @@
         <v>32.0</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="2"/>
       <c r="D41" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E41" s="3">
-        <v>2025.0</v>
+        <v>2026.0</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>107</v>
@@ -1675,13 +1772,13 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E42" s="3">
         <v>2025.0</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1">
@@ -1689,17 +1786,17 @@
         <v>34.0</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E43" s="3">
         <v>2025.0</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1">
@@ -1707,17 +1804,17 @@
         <v>35.0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E44" s="3">
         <v>2025.0</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1">
@@ -1725,17 +1822,17 @@
         <v>36.0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E45" s="3">
         <v>2025.0</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1">
@@ -1743,17 +1840,17 @@
         <v>37.0</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E46" s="3">
         <v>2025.0</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1">
@@ -1761,17 +1858,17 @@
         <v>38.0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E47" s="3">
         <v>2025.0</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1">
@@ -1779,17 +1876,17 @@
         <v>39.0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E48" s="3">
         <v>2025.0</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1">
@@ -1797,17 +1894,17 @@
         <v>40.0</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E49" s="3">
         <v>2025.0</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1">
@@ -1815,17 +1912,17 @@
         <v>41.0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E50" s="3">
         <v>2025.0</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1">
@@ -1833,17 +1930,17 @@
         <v>42.0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E51" s="3">
         <v>2025.0</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1">
@@ -1851,17 +1948,17 @@
         <v>43.0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E52" s="3">
         <v>2025.0</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1">
@@ -1869,17 +1966,17 @@
         <v>44.0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E53" s="3">
         <v>2025.0</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1">
@@ -1887,17 +1984,17 @@
         <v>45.0</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E54" s="3">
         <v>2025.0</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1">
@@ -1905,17 +2002,17 @@
         <v>46.0</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E55" s="3">
         <v>2025.0</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1">
@@ -1923,17 +2020,17 @@
         <v>47.0</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E56" s="3">
         <v>2025.0</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1">
@@ -1941,17 +2038,17 @@
         <v>48.0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E57" s="3">
         <v>2025.0</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1">
@@ -1959,17 +2056,17 @@
         <v>49.0</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E58" s="3">
         <v>2025.0</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1">
@@ -1977,17 +2074,17 @@
         <v>50.0</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E59" s="3">
         <v>2025.0</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1">
@@ -1995,17 +2092,17 @@
         <v>51.0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E60" s="3">
         <v>2025.0</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -2013,17 +2110,17 @@
         <v>52.0</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E61" s="3">
         <v>2025.0</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1">
@@ -2031,17 +2128,17 @@
         <v>53.0</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E62" s="3">
         <v>2025.0</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -2049,34 +2146,34 @@
         <v>54.0</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E63" s="3">
         <v>2025.0</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1">
       <c r="A64" s="3">
         <v>55.0</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>153</v>
       </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="E64" s="3">
-        <v>2023.0</v>
-      </c>
-      <c r="F64" s="4" t="s">
+        <v>2025.0</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2084,17 +2181,17 @@
       <c r="A65" s="3">
         <v>56.0</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="4" t="s">
-        <v>153</v>
+      <c r="C65" s="2"/>
+      <c r="D65" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="E65" s="3">
-        <v>2023.0</v>
-      </c>
-      <c r="F65" s="4" t="s">
+        <v>2025.0</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2102,113 +2199,158 @@
       <c r="A66" s="3">
         <v>57.0</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C66" s="5"/>
-      <c r="D66" s="4" t="s">
+      <c r="C66" s="2"/>
+      <c r="D66" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2025.0</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="E66" s="4">
-        <v>2025.0</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1">
       <c r="A67" s="3">
         <v>58.0</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C67" s="5"/>
-      <c r="D67" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E67" s="4">
+      <c r="E67" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" customHeight="1">
+      <c r="A68" s="3">
+        <v>59.0</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="D68" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68" s="3">
+        <v>2023.0</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" customHeight="1">
+      <c r="A69" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" s="6">
         <v>2025.0</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1"/>
-    <row r="69" ht="16.5" customHeight="1"/>
-    <row r="70" ht="16.5" customHeight="1"/>
+      <c r="F69" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" customHeight="1">
+      <c r="A70" s="3">
+        <v>61.0</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2025.0</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
     <row r="71" ht="16.5" customHeight="1"/>
     <row r="72" ht="16.5" customHeight="1"/>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="B74" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="B75" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
+    <row r="73" ht="16.5" customHeight="1"/>
+    <row r="74" ht="16.5" customHeight="1"/>
+    <row r="75" ht="16.5" customHeight="1"/>
     <row r="76" ht="16.5" customHeight="1">
-      <c r="B76" s="2"/>
-    </row>
-    <row r="77" ht="16.5" customHeight="1"/>
+      <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" customHeight="1">
+      <c r="B77" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
     <row r="78" ht="16.5" customHeight="1">
-      <c r="B78" s="2" t="s">
-        <v>166</v>
+      <c r="B78" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
-      <c r="B79" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="80" ht="16.5" customHeight="1">
-      <c r="B80" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1"/>
     <row r="81" ht="16.5" customHeight="1">
-      <c r="B81" s="3" t="s">
-        <v>169</v>
+      <c r="B81" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1">
       <c r="B82" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" ht="16.5" customHeight="1">
       <c r="B83" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1">
       <c r="B84" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" ht="16.5" customHeight="1">
       <c r="B85" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1">
-      <c r="B86" s="2"/>
+      <c r="B86" s="3" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
-      <c r="B87" s="2"/>
+      <c r="B87" s="3" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="88" ht="16.5" customHeight="1">
-      <c r="B88" s="2"/>
+      <c r="B88" s="3" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="89" ht="16.5" customHeight="1">
       <c r="B89" s="2"/>
@@ -2222,9 +2364,15 @@
     <row r="92" ht="16.5" customHeight="1">
       <c r="B92" s="2"/>
     </row>
-    <row r="93" ht="16.5" customHeight="1"/>
-    <row r="94" ht="16.5" customHeight="1"/>
-    <row r="95" ht="16.5" customHeight="1"/>
+    <row r="93" ht="16.5" customHeight="1">
+      <c r="B93" s="2"/>
+    </row>
+    <row r="94" ht="16.5" customHeight="1">
+      <c r="B94" s="2"/>
+    </row>
+    <row r="95" ht="16.5" customHeight="1">
+      <c r="B95" s="2"/>
+    </row>
     <row r="96" ht="16.5" customHeight="1"/>
     <row r="97" ht="16.5" customHeight="1"/>
     <row r="98" ht="16.5" customHeight="1"/>
@@ -3165,6 +3313,9 @@
     <row r="1033" ht="16.5" customHeight="1"/>
     <row r="1034" ht="16.5" customHeight="1"/>
     <row r="1035" ht="16.5" customHeight="1"/>
+    <row r="1036" ht="16.5" customHeight="1"/>
+    <row r="1037" ht="16.5" customHeight="1"/>
+    <row r="1038" ht="16.5" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -3185,267 +3336,267 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1"/>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1"/>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1"/>
     <row r="31" ht="16.5" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1"/>
     <row r="40" ht="16.5" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1"/>
     <row r="50" ht="16.5" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1"/>
